--- a/data/GPS/Metricas_GPS15.xlsx
+++ b/data/GPS/Metricas_GPS15.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30506"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E8B4AB-F992-44DD-A45C-8E09FDA77316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>eJy9lltv2jAUx7+KladVQhDCSuk0TWJDfVnLaKe26y6qjO0QF1+i2C4tiO8+27A2yYCVTM1Tck6Oz/n9j29ZBBhqooJ3YBFo6R/OYV+CKIy64XF4FDRAcA+ZczEXq4Ol9cSZ5C8Nd/HpvUbxxBX6sVgbtxS7KG4MhnPa7c3cUCTZOsi+rSPmYkbdtxTqxNm+pLX1Y0rytoDc2ycEJdA5jKDaORxxPiELrVb7narbiaePIVPEOjKCDfI5tNS+BJxgEq+GtbuHxx3rI8Jw6/GYv3JYqVRNkqI8mR2e5+BU5DkHJoOISlHGO4HnV3m9Pj6XNWXwkWT5TEPJxxnZJfn7RfQpKMJS7WrvzDuyUWgdtS0zpuZuYzPHmVEJeWrTf/cWU7Wjt1NeaC1VGgpEIbDF7GosMX9OrnsFZp2Z10CeC9J8WxH8A2j3wJS3kjL8adckdcF3K8Jb+uiwEYGNAr7wy7O6BBxVFOD6H/Uavc0KziV8qG8KkNA7FBTOgZ8mDMcQfE0zKrQCb94/z8LBX+tIfOzXIQIi5HREFXT0EWFkdUhaoBJ/++JbLZsYk8r8A6LgLgmXQ3Wz39nJVwuvwhw0/wzdcje1VEvlNfRRE5zBB8phmRqNCN6TenXxVaKmYh/qAdmKncadTi3NVin+R7PdfixctFceukw8iG6Gr3610jvVZBK/cGWP/D8COJUQB0uXBjFKhF6VEoYx73zaB2QGrmU2HUs5DZa/ATFnEHA=</t>
   </si>
@@ -123,9 +132,6 @@
   </si>
   <si>
     <t xml:space="preserve">Juan_Manuel_Ruiz </t>
-  </si>
-  <si>
-    <t>Denfensa Lateral</t>
   </si>
   <si>
     <t xml:space="preserve">jingshuo_wang </t>
@@ -134,25 +140,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -163,38 +170,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -202,7 +214,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -392,26 +404,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="133.25"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="133.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -420,21 +435,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -481,12 +497,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B2" s="2">
-        <v>44.167</v>
+        <v>44.167000000000002</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>18</v>
@@ -495,45 +511,45 @@
         <v>19</v>
       </c>
       <c r="E2" s="2">
-        <v>2.215</v>
+        <v>2.2149999999999999</v>
       </c>
       <c r="F2" s="2">
-        <v>0.258</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="H2" s="2">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="L2" s="2">
         <v>6.476</v>
       </c>
       <c r="M2" s="2">
-        <v>-5.243</v>
+        <v>-5.2430000000000003</v>
       </c>
       <c r="N2" s="2">
         <v>29.567</v>
       </c>
       <c r="O2" s="2">
-        <v>354.829</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>354.82900000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B3" s="2">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
@@ -542,42 +558,42 @@
         <v>21</v>
       </c>
       <c r="E3" s="2">
-        <v>2.586</v>
+        <v>2.5859999999999999</v>
       </c>
       <c r="F3" s="2">
-        <v>0.295</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="G3" s="2">
         <v>0.106</v>
       </c>
       <c r="H3" s="2">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="I3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J3" s="2">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="K3" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="L3" s="2">
-        <v>5.846</v>
+        <v>5.8460000000000001</v>
       </c>
       <c r="M3" s="2">
-        <v>-6.546</v>
+        <v>-6.5460000000000003</v>
       </c>
       <c r="N3" s="2">
         <v>30.73</v>
       </c>
       <c r="O3" s="2">
-        <v>524.703</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>524.70299999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B4" s="2">
         <v>46.817</v>
@@ -586,48 +602,48 @@
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2">
-        <v>2.788</v>
+        <v>2.7879999999999998</v>
       </c>
       <c r="F4" s="2">
-        <v>0.472</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="G4" s="2">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H4" s="2">
-        <v>0.013</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="I4" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K4" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="L4" s="2">
-        <v>5.699</v>
+        <v>5.6989999999999998</v>
       </c>
       <c r="M4" s="2">
         <v>-5.875</v>
       </c>
       <c r="N4" s="2">
-        <v>29.812</v>
+        <v>29.812000000000001</v>
       </c>
       <c r="O4" s="2">
-        <v>552.422</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>552.42200000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B5" s="2">
-        <v>45.017</v>
+        <v>45.017000000000003</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>23</v>
@@ -639,39 +655,39 @@
         <v>2.133</v>
       </c>
       <c r="F5" s="2">
-        <v>0.267</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="G5" s="2">
-        <v>0.047</v>
+        <v>4.7E-2</v>
       </c>
       <c r="H5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L5" s="2">
-        <v>5.626</v>
+        <v>5.6260000000000003</v>
       </c>
       <c r="M5" s="2">
-        <v>-4.764</v>
+        <v>-4.7640000000000002</v>
       </c>
       <c r="N5" s="2">
-        <v>28.411</v>
+        <v>28.411000000000001</v>
       </c>
       <c r="O5" s="2">
         <v>136.637</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B6" s="2">
         <v>53.25</v>
@@ -683,45 +699,45 @@
         <v>26</v>
       </c>
       <c r="E6" s="2">
-        <v>3.231</v>
+        <v>3.2309999999999999</v>
       </c>
       <c r="F6" s="2">
-        <v>0.547</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="G6" s="2">
-        <v>0.085</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="H6" s="2">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I6" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K6" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="L6" s="2">
-        <v>5.687</v>
+        <v>5.6870000000000003</v>
       </c>
       <c r="M6" s="2">
-        <v>-6.447</v>
+        <v>-6.4470000000000001</v>
       </c>
       <c r="N6" s="2">
-        <v>29.117</v>
+        <v>29.117000000000001</v>
       </c>
       <c r="O6" s="2">
         <v>478.178</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B7" s="2">
-        <v>46.717</v>
+        <v>46.716999999999999</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>27</v>
@@ -733,42 +749,42 @@
         <v>2.552</v>
       </c>
       <c r="F7" s="2">
-        <v>0.287</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="G7" s="2">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="H7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="K7" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="2">
-        <v>4.982</v>
+        <v>4.9820000000000002</v>
       </c>
       <c r="M7" s="2">
         <v>-6.492</v>
       </c>
       <c r="N7" s="2">
-        <v>28.498</v>
+        <v>28.498000000000001</v>
       </c>
       <c r="O7" s="2">
-        <v>491.466</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>491.46600000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B8" s="2">
-        <v>50.717</v>
+        <v>50.716999999999999</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -777,42 +793,42 @@
         <v>30</v>
       </c>
       <c r="E8" s="2">
-        <v>2.663</v>
+        <v>2.6629999999999998</v>
       </c>
       <c r="F8" s="2">
-        <v>0.403</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="G8" s="2">
-        <v>0.088</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="H8" s="2">
-        <v>0.017</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="I8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="2">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="L8" s="2">
-        <v>6.285</v>
+        <v>6.2850000000000001</v>
       </c>
       <c r="M8" s="2">
-        <v>-7.088</v>
+        <v>-7.0880000000000001</v>
       </c>
       <c r="N8" s="2">
-        <v>30.269</v>
+        <v>30.268999999999998</v>
       </c>
       <c r="O8" s="2">
-        <v>440.628</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>440.62799999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B9" s="2">
         <v>49.817</v>
@@ -824,42 +840,42 @@
         <v>26</v>
       </c>
       <c r="E9" s="2">
-        <v>2.398</v>
+        <v>2.3980000000000001</v>
       </c>
       <c r="F9" s="2">
         <v>0.127</v>
       </c>
       <c r="G9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="K9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L9" s="2">
-        <v>4.072</v>
+        <v>4.0720000000000001</v>
       </c>
       <c r="M9" s="2">
-        <v>-4.656</v>
+        <v>-4.6559999999999997</v>
       </c>
       <c r="N9" s="2">
-        <v>21.841</v>
+        <v>21.841000000000001</v>
       </c>
       <c r="O9" s="2">
-        <v>458.671</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>458.67099999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B10" s="2">
         <v>52.067</v>
@@ -871,42 +887,42 @@
         <v>30</v>
       </c>
       <c r="E10" s="2">
-        <v>2.769</v>
+        <v>2.7690000000000001</v>
       </c>
       <c r="F10" s="2">
-        <v>0.526</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="G10" s="2">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="H10" s="2">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K10" s="2">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="L10" s="2">
-        <v>5.606</v>
+        <v>5.6059999999999999</v>
       </c>
       <c r="M10" s="2">
-        <v>-6.829</v>
+        <v>-6.8289999999999997</v>
       </c>
       <c r="N10" s="2">
         <v>29.311</v>
       </c>
       <c r="O10" s="2">
-        <v>491.235</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>491.23500000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B11" s="2">
         <v>46.25</v>
@@ -918,28 +934,28 @@
         <v>21</v>
       </c>
       <c r="E11" s="2">
-        <v>2.924</v>
+        <v>2.9239999999999999</v>
       </c>
       <c r="F11" s="2">
-        <v>0.512</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="G11" s="2">
-        <v>0.078</v>
+        <v>7.8E-2</v>
       </c>
       <c r="H11" s="2">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="I11" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="L11" s="2">
-        <v>5.917</v>
+        <v>5.9169999999999998</v>
       </c>
       <c r="M11" s="2">
         <v>-5.835</v>
@@ -948,15 +964,15 @@
         <v>28.901</v>
       </c>
       <c r="O11" s="2">
-        <v>607.372</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>607.37199999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B12" s="2">
-        <v>44.533</v>
+        <v>44.533000000000001</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
@@ -968,75 +984,75 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="2">
-        <v>0.586</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="G12" s="2">
-        <v>0.087</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="H12" s="2">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I12" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="2">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="K12" s="2">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="L12" s="2">
         <v>5.306</v>
       </c>
       <c r="M12" s="2">
-        <v>-4.936</v>
+        <v>-4.9359999999999999</v>
       </c>
       <c r="N12" s="2">
-        <v>29.347</v>
+        <v>29.347000000000001</v>
       </c>
       <c r="O12" s="2">
-        <v>523.479</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>523.47900000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B13" s="2">
-        <v>53.467</v>
+        <v>53.466999999999999</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2">
-        <v>2.622</v>
+        <v>2.6219999999999999</v>
       </c>
       <c r="F13" s="2">
         <v>0.497</v>
       </c>
       <c r="G13" s="2">
-        <v>0.044</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="H13" s="2">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="I13" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="K13" s="2">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="L13" s="2">
-        <v>5.473</v>
+        <v>5.4729999999999999</v>
       </c>
       <c r="M13" s="2">
-        <v>-6.721</v>
+        <v>-6.7210000000000001</v>
       </c>
       <c r="N13" s="2">
         <v>29.462</v>
@@ -1045,54 +1061,54 @@
         <v>445.01</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="B14" s="2">
         <v>54.6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="2">
-        <v>3.369</v>
+        <v>3.3690000000000002</v>
       </c>
       <c r="F14" s="2">
-        <v>0.461</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="G14" s="2">
         <v>0.05</v>
       </c>
       <c r="H14" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K14" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2">
-        <v>6.283</v>
+        <v>6.2830000000000004</v>
       </c>
       <c r="M14" s="2">
-        <v>-5.895</v>
+        <v>-5.8949999999999996</v>
       </c>
       <c r="N14" s="2">
         <v>28.31</v>
       </c>
       <c r="O14" s="2">
-        <v>689.341</v>
+        <v>689.34100000000001</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>